--- a/New BTS/Edit/Item code _edit _site wise_final.xlsx
+++ b/New BTS/Edit/Item code _edit _site wise_final.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7500" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7500"/>
   </bookViews>
   <sheets>
     <sheet name="RULES" sheetId="2" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="39">
   <si>
     <t>Plant</t>
   </si>
@@ -126,23 +126,29 @@
     <t>TOLL</t>
   </si>
   <si>
-    <t>BBU5900 Box</t>
-  </si>
-  <si>
     <t>BBU</t>
   </si>
   <si>
     <t>Embedded Environment Monitoring Unit (with sensors)</t>
   </si>
   <si>
-    <t>CGKTL18</t>
+    <t>CGKTLL9</t>
+  </si>
+  <si>
+    <t>CGKTL07</t>
+  </si>
+  <si>
+    <t>BB6630 incl Port HWAC</t>
+  </si>
+  <si>
+    <t>SFP ONLY</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -211,10 +217,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Ericsson Hilda"/>
     </font>
   </fonts>
   <fills count="7">
@@ -389,9 +391,8 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -400,7 +401,12 @@
     <cellStyle name="Normal 3 2 2 2" xfId="3"/>
     <cellStyle name="Normal 3 3" xfId="1"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="11">
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color theme="0"/>
@@ -771,8 +777,8 @@
       <c r="A2" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="8">
-        <v>2076603</v>
+      <c r="B2" s="1">
+        <v>2076992</v>
       </c>
       <c r="C2" s="16">
         <v>909090</v>
@@ -780,17 +786,17 @@
       <c r="D2" s="2">
         <v>9000</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="24" t="s">
+      <c r="G2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H2" s="16" t="s">
         <v>33</v>
-      </c>
-      <c r="H2" s="16" t="s">
-        <v>34</v>
       </c>
       <c r="J2" s="17"/>
     </row>
@@ -807,14 +813,14 @@
       <c r="D3" s="2">
         <v>9000</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="24" t="s">
-        <v>35</v>
+      <c r="G3" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="H3" s="16" t="s">
         <v>32</v>
@@ -824,7 +830,7 @@
       <c r="A4" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4" s="24">
         <v>2073640</v>
       </c>
       <c r="C4" s="16">
@@ -833,13 +839,13 @@
       <c r="D4" s="2">
         <v>9000</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="G4" s="3" t="s">
         <v>21</v>
       </c>
       <c r="H4" s="16" t="s">
@@ -899,7 +905,9 @@
       <c r="B7" s="4">
         <v>8001923</v>
       </c>
-      <c r="C7" s="16"/>
+      <c r="C7" s="16">
+        <v>88888</v>
+      </c>
       <c r="D7" s="4">
         <v>9000</v>
       </c>
@@ -912,7 +920,9 @@
       <c r="G7" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="16"/>
+      <c r="H7" s="16" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="8" spans="1:10" ht="15.75">
       <c r="A8" s="12" t="s">
@@ -1080,53 +1090,38 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C3">
-    <cfRule type="containsErrors" dxfId="9" priority="41">
+    <cfRule type="containsErrors" dxfId="10" priority="42">
       <formula>ISERROR(C3)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2">
-    <cfRule type="containsErrors" dxfId="8" priority="24">
+    <cfRule type="containsErrors" dxfId="9" priority="25">
       <formula>ISERROR(C2)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G5:G8">
-    <cfRule type="containsErrors" dxfId="7" priority="23">
+    <cfRule type="containsErrors" dxfId="8" priority="24">
       <formula>ISERROR(G5)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C15">
-    <cfRule type="containsErrors" dxfId="6" priority="18">
+    <cfRule type="containsErrors" dxfId="7" priority="19">
       <formula>ISERROR(C4)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H15">
-    <cfRule type="containsErrors" dxfId="5" priority="17">
+    <cfRule type="containsErrors" dxfId="6" priority="18">
       <formula>ISERROR(H2)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2">
-    <cfRule type="containsErrors" dxfId="4" priority="7">
-      <formula>ISERROR(B2)</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B3">
-    <cfRule type="containsErrors" dxfId="3" priority="4">
+    <cfRule type="containsErrors" dxfId="4" priority="5">
       <formula>ISERROR(B3)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2">
-    <cfRule type="containsErrors" dxfId="2" priority="3">
-      <formula>ISERROR(G2)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G2">
-    <cfRule type="containsErrors" dxfId="1" priority="2">
-      <formula>ISERROR(G2)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G3">
+  <conditionalFormatting sqref="E3:G4 E2:F2">
     <cfRule type="containsErrors" dxfId="0" priority="1">
-      <formula>ISERROR(G3)</formula>
+      <formula>ISERROR(E2)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1149,12 +1144,14 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="E2" s="18"/>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="E2" s="18"/>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="23"/>
       <c r="E3" s="18"/>
     </row>
     <row r="4" spans="1:5">
